--- a/doc/kv_script_conv_position_data.xlsx
+++ b/doc/kv_script_conv_position_data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tk\prj\hg-0025-0016\git\kv-x520\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869975E7-73BE-4E8B-9382-E38004ACD90D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DAFC47A-B32D-4849-808A-F37D1039C0D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-165" yWindow="-165" windowWidth="29130" windowHeight="15810" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{181063BD-94E1-4A36-8B86-700C2293C5C2}"/>
   </bookViews>
   <sheets>
     <sheet name="info_index" sheetId="1" r:id="rId1"/>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="B3" t="str" cm="1">
         <f t="array" aca="1" ref="B3" ca="1">CELL("filename")</f>
-        <v>C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_position_data.xlsx]info_index</v>
+        <v>C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_position_data.xlsx]info_index</v>
       </c>
       <c r="E3" t="s">
         <v>49</v>
@@ -3893,7 +3893,7 @@
       </c>
       <c r="B5" t="str">
         <f ca="1">"このスクリプトは "&amp;B3&amp;" によって生成されました。"</f>
-        <v>このスクリプトは C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_position_data.xlsx]info_index によって生成されました。</v>
+        <v>このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_position_data.xlsx]info_index によって生成されました。</v>
       </c>
       <c r="E5" t="str">
         <f t="shared" ref="E5:E68" si="0">E4</f>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="B13" t="str">
         <f ca="1">$AK$205</f>
-        <v>//このスクリプトは C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_position_data.xlsx]info_index によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_position_data.xlsx]info_index によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸
@@ -24932,7 +24932,7 @@
     <row r="205" spans="5:37" x14ac:dyDescent="0.55000000000000004">
       <c r="AK205" t="str">
         <f ca="1">IF(LENB($B$5),$B$7&amp;$B$5,"")&amp;CHAR(10)&amp;_xlfn.CONCAT(AK$3:AK$202)&amp;CHAR(10)&amp;"ELSE"&amp;CHAR(10)&amp;CHAR(9)&amp;$B$29&amp;CHAR(9)&amp;$B$8&amp;" 1"&amp;$B$9&amp;CHAR(10)&amp;"END_IF;"&amp;IF(LENB($B$6),CHAR(10)&amp;$B$7&amp;$B$6,"")</f>
-        <v>//このスクリプトは C:\tk\proj\gpg-0007_自動コア巻き\git\kv-x520\doc\[kv_script_conv_position_data.xlsx]info_index によって生成されました。
+        <v>//このスクリプトは C:\tk\prj\hg-0025-0016\git\kv-x520\doc\[kv_script_conv_position_data.xlsx]info_index によって生成されました。
 //axis
 IF strInfoType = 'axis' THEN
 	//箔ロウリール軸
